--- a/notas2026.xlsx
+++ b/notas2026.xlsx
@@ -20755,7 +20755,7 @@
         <v>4</v>
       </c>
       <c r="H105">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="T105">
         <v>2</v>
@@ -20910,7 +20910,7 @@
         </is>
       </c>
       <c r="CD105">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="CE105" t="inlineStr">
         <is>
